--- a/exammarks1ds_format.xlsx
+++ b/exammarks1ds_format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Campus_technology\excel scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Campus_technology\backend-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202E84EE-0A34-4A8A-9967-698F2F406435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B72E66-C01C-48C9-A341-9ED2039BD2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11869" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11844" uniqueCount="1100">
   <si>
     <t>name</t>
   </si>
@@ -3708,12 +3708,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q870"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="2" max="2" width="29.25" customWidth="1"/>
+    <col min="4" max="4" width="27.0625" customWidth="1"/>
+    <col min="11" max="11" width="30.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3766,7 +3768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>1096</v>
       </c>
@@ -3819,7 +3821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>1096</v>
       </c>
@@ -3872,7 +3874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>1096</v>
       </c>
@@ -3925,7 +3927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>1096</v>
       </c>
@@ -3978,7 +3980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>1096</v>
       </c>
@@ -4031,7 +4033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>1096</v>
       </c>
@@ -4084,7 +4086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>1096</v>
       </c>
@@ -4137,7 +4139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>1096</v>
       </c>
@@ -4190,7 +4192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>1096</v>
       </c>
@@ -4243,7 +4245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>1096</v>
       </c>
@@ -4296,7 +4298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>1096</v>
       </c>
@@ -4349,7 +4351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>1096</v>
       </c>
@@ -4402,7 +4404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>1096</v>
       </c>
@@ -4455,7 +4457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>1096</v>
       </c>
@@ -4508,7 +4510,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>1096</v>
       </c>
@@ -4561,7 +4563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>1096</v>
       </c>
@@ -4614,7 +4616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>1096</v>
       </c>
@@ -4667,7 +4669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>1096</v>
       </c>
@@ -4720,7 +4722,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>1096</v>
       </c>
@@ -4773,7 +4775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>1096</v>
       </c>
@@ -4826,7 +4828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>1096</v>
       </c>
@@ -4879,7 +4881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>1096</v>
       </c>
@@ -4932,7 +4934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>1096</v>
       </c>
@@ -4985,7 +4987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
         <v>1096</v>
       </c>
@@ -5038,7 +5040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>1096</v>
       </c>
@@ -5091,7 +5093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>1096</v>
       </c>
@@ -5144,7 +5146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>1096</v>
       </c>
@@ -5197,7 +5199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>1096</v>
       </c>
@@ -5250,7 +5252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>1096</v>
       </c>
@@ -5303,7 +5305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>1096</v>
       </c>
@@ -5356,7 +5358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>1096</v>
       </c>
@@ -5409,7 +5411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
         <v>1096</v>
       </c>
@@ -5462,7 +5464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
         <v>1096</v>
       </c>
@@ -5515,7 +5517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
         <v>1096</v>
       </c>
@@ -5568,7 +5570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
         <v>1096</v>
       </c>
@@ -5621,7 +5623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
         <v>1096</v>
       </c>
@@ -5674,7 +5676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
         <v>1096</v>
       </c>
@@ -5727,7 +5729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
         <v>1096</v>
       </c>
@@ -5780,7 +5782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
         <v>1096</v>
       </c>
@@ -5833,7 +5835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
         <v>1096</v>
       </c>
@@ -5886,7 +5888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
         <v>1096</v>
       </c>
@@ -5939,7 +5941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>1096</v>
       </c>
@@ -5992,7 +5994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
         <v>1096</v>
       </c>
@@ -6045,7 +6047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
         <v>1096</v>
       </c>
@@ -6098,7 +6100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
         <v>1096</v>
       </c>
@@ -6151,7 +6153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
         <v>1096</v>
       </c>
@@ -6204,7 +6206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
         <v>1096</v>
       </c>
@@ -6257,7 +6259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
         <v>1096</v>
       </c>
@@ -6310,7 +6312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
         <v>1096</v>
       </c>
@@ -6363,7 +6365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
         <v>1096</v>
       </c>
@@ -6416,7 +6418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
         <v>1096</v>
       </c>
@@ -6469,7 +6471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
         <v>1096</v>
       </c>
@@ -6522,7 +6524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
         <v>1096</v>
       </c>
@@ -6575,7 +6577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>1096</v>
       </c>
@@ -6628,7 +6630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
         <v>1096</v>
       </c>
@@ -6681,7 +6683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
         <v>1096</v>
       </c>
@@ -6734,7 +6736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
         <v>1096</v>
       </c>
@@ -6787,7 +6789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
         <v>1096</v>
       </c>
@@ -6840,7 +6842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
         <v>1096</v>
       </c>
@@ -6893,7 +6895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
         <v>1096</v>
       </c>
@@ -6946,7 +6948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
         <v>1096</v>
       </c>
@@ -6999,7 +7001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
         <v>1096</v>
       </c>
@@ -7052,7 +7054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
         <v>1096</v>
       </c>
@@ -7105,7 +7107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
         <v>1096</v>
       </c>
@@ -7158,7 +7160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
         <v>1096</v>
       </c>
@@ -7211,7 +7213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
         <v>1096</v>
       </c>
@@ -7264,7 +7266,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
         <v>1096</v>
       </c>
@@ -7317,7 +7319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
         <v>1096</v>
       </c>
@@ -7370,7 +7372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
         <v>1096</v>
       </c>
@@ -7423,7 +7425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
         <v>1096</v>
       </c>
@@ -7476,7 +7478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
         <v>1096</v>
       </c>
@@ -7529,7 +7531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
         <v>1096</v>
       </c>
@@ -7582,7 +7584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
         <v>1096</v>
       </c>
@@ -7635,7 +7637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
         <v>1096</v>
       </c>
@@ -7688,7 +7690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
         <v>1096</v>
       </c>
@@ -7741,7 +7743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
         <v>1096</v>
       </c>
@@ -7794,7 +7796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
         <v>1096</v>
       </c>
@@ -7847,7 +7849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
         <v>1096</v>
       </c>
@@ -7900,7 +7902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
         <v>1096</v>
       </c>
@@ -7953,7 +7955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
         <v>1096</v>
       </c>
@@ -8006,7 +8008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
         <v>1096</v>
       </c>
@@ -8059,7 +8061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
         <v>1096</v>
       </c>
@@ -8112,7 +8114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
         <v>1096</v>
       </c>
@@ -8165,7 +8167,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
         <v>1096</v>
       </c>
@@ -8218,7 +8220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
         <v>1096</v>
       </c>
@@ -8271,7 +8273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
         <v>1096</v>
       </c>
@@ -8324,7 +8326,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
         <v>1096</v>
       </c>
@@ -8377,7 +8379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
         <v>1096</v>
       </c>
@@ -8430,7 +8432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
         <v>1096</v>
       </c>
@@ -8483,7 +8485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
         <v>1096</v>
       </c>
@@ -8536,7 +8538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
         <v>1096</v>
       </c>
@@ -8589,7 +8591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
         <v>1096</v>
       </c>
@@ -8642,7 +8644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
         <v>1096</v>
       </c>
@@ -8695,7 +8697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
         <v>1096</v>
       </c>
@@ -8748,7 +8750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
         <v>1096</v>
       </c>
@@ -8801,7 +8803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
         <v>1096</v>
       </c>
@@ -8854,7 +8856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
         <v>1096</v>
       </c>
@@ -8907,7 +8909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
         <v>1096</v>
       </c>
@@ -8960,7 +8962,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
         <v>1096</v>
       </c>
@@ -9013,7 +9015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
         <v>1096</v>
       </c>
@@ -9066,7 +9068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
         <v>1096</v>
       </c>
@@ -9119,7 +9121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
         <v>1096</v>
       </c>
@@ -9172,7 +9174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
         <v>1096</v>
       </c>
@@ -9225,7 +9227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
         <v>1096</v>
       </c>
@@ -9278,7 +9280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
         <v>1096</v>
       </c>
@@ -9331,7 +9333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
         <v>1096</v>
       </c>
@@ -9384,7 +9386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
         <v>1096</v>
       </c>
@@ -9437,7 +9439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
         <v>1096</v>
       </c>
@@ -9490,7 +9492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
         <v>1096</v>
       </c>
@@ -9543,7 +9545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
         <v>1096</v>
       </c>
@@ -9596,7 +9598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
         <v>1096</v>
       </c>
@@ -9649,7 +9651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
         <v>1096</v>
       </c>
@@ -9702,7 +9704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
         <v>1096</v>
       </c>
@@ -9755,7 +9757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
         <v>1096</v>
       </c>
@@ -9808,7 +9810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
         <v>1096</v>
       </c>
@@ -9861,7 +9863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
         <v>1096</v>
       </c>
@@ -9914,7 +9916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
         <v>1096</v>
       </c>
@@ -9967,7 +9969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
         <v>1096</v>
       </c>
@@ -10020,7 +10022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
         <v>1096</v>
       </c>
@@ -10073,7 +10075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
         <v>1096</v>
       </c>
@@ -10126,7 +10128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
         <v>1096</v>
       </c>
@@ -10179,7 +10181,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
         <v>1096</v>
       </c>
@@ -10232,7 +10234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
         <v>1096</v>
       </c>
@@ -10285,7 +10287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
         <v>1096</v>
       </c>
@@ -10338,7 +10340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
         <v>1096</v>
       </c>
@@ -10391,7 +10393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
         <v>1096</v>
       </c>
@@ -10444,7 +10446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
         <v>1096</v>
       </c>
@@ -10497,7 +10499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
         <v>1096</v>
       </c>
@@ -10550,7 +10552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
         <v>1096</v>
       </c>
@@ -10603,7 +10605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
         <v>1096</v>
       </c>
@@ -10656,7 +10658,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A132" t="s">
         <v>1096</v>
       </c>
@@ -10709,7 +10711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A133" t="s">
         <v>1096</v>
       </c>
@@ -10762,7 +10764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A134" t="s">
         <v>1096</v>
       </c>
@@ -10815,7 +10817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A135" t="s">
         <v>1096</v>
       </c>
@@ -10868,7 +10870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A136" t="s">
         <v>1096</v>
       </c>
@@ -10921,7 +10923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A137" t="s">
         <v>1096</v>
       </c>
@@ -10974,7 +10976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A138" t="s">
         <v>1096</v>
       </c>
@@ -11027,7 +11029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A139" t="s">
         <v>1096</v>
       </c>
@@ -11080,7 +11082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A140" t="s">
         <v>1096</v>
       </c>
@@ -11133,7 +11135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A141" t="s">
         <v>1096</v>
       </c>
@@ -11186,7 +11188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A142" t="s">
         <v>1096</v>
       </c>
@@ -11239,7 +11241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A143" t="s">
         <v>1096</v>
       </c>
@@ -11292,7 +11294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A144" t="s">
         <v>1096</v>
       </c>
@@ -11345,7 +11347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A145" t="s">
         <v>1096</v>
       </c>
@@ -11398,7 +11400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A146" t="s">
         <v>1096</v>
       </c>
@@ -11451,7 +11453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A147" t="s">
         <v>1096</v>
       </c>
@@ -11504,7 +11506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A148" t="s">
         <v>1096</v>
       </c>
@@ -11557,7 +11559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A149" t="s">
         <v>1096</v>
       </c>
@@ -11610,7 +11612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A150" t="s">
         <v>1096</v>
       </c>
@@ -11663,7 +11665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A151" t="s">
         <v>1096</v>
       </c>
@@ -11716,7 +11718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A152" t="s">
         <v>1096</v>
       </c>
@@ -11769,7 +11771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A153" t="s">
         <v>1096</v>
       </c>
@@ -11822,7 +11824,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A154" t="s">
         <v>1096</v>
       </c>
@@ -11875,7 +11877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A155" t="s">
         <v>1096</v>
       </c>
@@ -11928,7 +11930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A156" t="s">
         <v>1096</v>
       </c>
@@ -11981,7 +11983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A157" t="s">
         <v>1096</v>
       </c>
@@ -12034,7 +12036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A158" t="s">
         <v>1096</v>
       </c>
@@ -12087,7 +12089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A159" t="s">
         <v>1096</v>
       </c>
@@ -12140,7 +12142,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A160" t="s">
         <v>1096</v>
       </c>
@@ -12193,7 +12195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A161" t="s">
         <v>1096</v>
       </c>
@@ -12246,7 +12248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A162" t="s">
         <v>1096</v>
       </c>
@@ -12299,7 +12301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A163" t="s">
         <v>1096</v>
       </c>
@@ -12352,7 +12354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A164" t="s">
         <v>1096</v>
       </c>
@@ -12405,7 +12407,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A165" t="s">
         <v>1096</v>
       </c>
@@ -12458,7 +12460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A166" t="s">
         <v>1096</v>
       </c>
@@ -12511,7 +12513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A167" t="s">
         <v>1096</v>
       </c>
@@ -12564,7 +12566,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A168" t="s">
         <v>1096</v>
       </c>
@@ -12617,7 +12619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A169" t="s">
         <v>1096</v>
       </c>
@@ -12670,7 +12672,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A170" t="s">
         <v>1096</v>
       </c>
@@ -12723,7 +12725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A171" t="s">
         <v>1096</v>
       </c>
@@ -12776,7 +12778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A172" t="s">
         <v>1096</v>
       </c>
@@ -12829,7 +12831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A173" t="s">
         <v>1096</v>
       </c>
@@ -12882,7 +12884,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A174" t="s">
         <v>1096</v>
       </c>
@@ -12935,7 +12937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A175" t="s">
         <v>1096</v>
       </c>
@@ -12988,7 +12990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A176" t="s">
         <v>1096</v>
       </c>
@@ -13041,7 +13043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A177" t="s">
         <v>1096</v>
       </c>
@@ -13094,7 +13096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A178" t="s">
         <v>1096</v>
       </c>
@@ -13147,7 +13149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A179" t="s">
         <v>1096</v>
       </c>
@@ -13200,7 +13202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A180" t="s">
         <v>1096</v>
       </c>
@@ -13253,7 +13255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A181" t="s">
         <v>1096</v>
       </c>
@@ -13306,7 +13308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A182" t="s">
         <v>1096</v>
       </c>
@@ -13359,7 +13361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A183" t="s">
         <v>1096</v>
       </c>
@@ -13412,7 +13414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A184" t="s">
         <v>1096</v>
       </c>
@@ -13465,7 +13467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A185" t="s">
         <v>1096</v>
       </c>
@@ -13518,7 +13520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A186" t="s">
         <v>1096</v>
       </c>
@@ -13571,7 +13573,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A187" t="s">
         <v>1096</v>
       </c>
@@ -13624,7 +13626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A188" t="s">
         <v>1096</v>
       </c>
@@ -13677,7 +13679,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A189" t="s">
         <v>1096</v>
       </c>
@@ -13730,7 +13732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A190" t="s">
         <v>1096</v>
       </c>
@@ -13783,7 +13785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A191" t="s">
         <v>1096</v>
       </c>
@@ -13836,7 +13838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A192" t="s">
         <v>1096</v>
       </c>
@@ -13889,7 +13891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A193" t="s">
         <v>1096</v>
       </c>
@@ -13942,7 +13944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A194" t="s">
         <v>1096</v>
       </c>
@@ -13995,7 +13997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A195" t="s">
         <v>1096</v>
       </c>
@@ -14048,7 +14050,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A196" t="s">
         <v>1096</v>
       </c>
@@ -14101,7 +14103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A197" t="s">
         <v>1096</v>
       </c>
@@ -14154,7 +14156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A198" t="s">
         <v>1096</v>
       </c>
@@ -14207,7 +14209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A199" t="s">
         <v>1096</v>
       </c>
@@ -14260,7 +14262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A200" t="s">
         <v>1096</v>
       </c>
@@ -14313,7 +14315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A201" t="s">
         <v>1096</v>
       </c>
@@ -14366,7 +14368,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A202" t="s">
         <v>1096</v>
       </c>
@@ -14419,7 +14421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A203" t="s">
         <v>1096</v>
       </c>
@@ -14472,7 +14474,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A204" t="s">
         <v>1096</v>
       </c>
@@ -14525,7 +14527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A205" t="s">
         <v>1096</v>
       </c>
@@ -14578,7 +14580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A206" t="s">
         <v>1096</v>
       </c>
@@ -14631,7 +14633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A207" t="s">
         <v>1096</v>
       </c>
@@ -14684,7 +14686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A208" t="s">
         <v>1096</v>
       </c>
@@ -14737,7 +14739,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A209" t="s">
         <v>1096</v>
       </c>
@@ -14790,7 +14792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A210" t="s">
         <v>1096</v>
       </c>
@@ -14843,7 +14845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A211" t="s">
         <v>1096</v>
       </c>
@@ -14896,7 +14898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A212" t="s">
         <v>1096</v>
       </c>
@@ -14949,7 +14951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A213" t="s">
         <v>1096</v>
       </c>
@@ -15002,7 +15004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A214" t="s">
         <v>1096</v>
       </c>
@@ -15055,7 +15057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A215" t="s">
         <v>1096</v>
       </c>
@@ -15108,7 +15110,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A216" t="s">
         <v>1096</v>
       </c>
@@ -15161,7 +15163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A217" t="s">
         <v>1096</v>
       </c>
@@ -15214,7 +15216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A218" t="s">
         <v>1096</v>
       </c>
@@ -15267,7 +15269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A219" t="s">
         <v>1096</v>
       </c>
@@ -15320,7 +15322,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A220" t="s">
         <v>1096</v>
       </c>
@@ -15373,7 +15375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A221" t="s">
         <v>1096</v>
       </c>
@@ -15426,7 +15428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A222" t="s">
         <v>1096</v>
       </c>
@@ -15479,7 +15481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A223" t="s">
         <v>1096</v>
       </c>
@@ -15532,7 +15534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A224" t="s">
         <v>1096</v>
       </c>
@@ -15585,7 +15587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A225" t="s">
         <v>1096</v>
       </c>
@@ -15638,7 +15640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A226" t="s">
         <v>1096</v>
       </c>
@@ -15691,7 +15693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A227" t="s">
         <v>1096</v>
       </c>
@@ -15744,7 +15746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A228" t="s">
         <v>1096</v>
       </c>
@@ -15797,7 +15799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A229" t="s">
         <v>1096</v>
       </c>
@@ -15850,7 +15852,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A230" t="s">
         <v>1096</v>
       </c>
@@ -15903,7 +15905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A231" t="s">
         <v>1096</v>
       </c>
@@ -15956,7 +15958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A232" t="s">
         <v>1096</v>
       </c>
@@ -16009,7 +16011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A233" t="s">
         <v>1096</v>
       </c>
@@ -16062,7 +16064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A234" t="s">
         <v>1096</v>
       </c>
@@ -16115,7 +16117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A235" t="s">
         <v>1096</v>
       </c>
@@ -16168,7 +16170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A236" t="s">
         <v>1096</v>
       </c>
@@ -16221,7 +16223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A237" t="s">
         <v>1096</v>
       </c>
@@ -16274,7 +16276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A238" t="s">
         <v>1096</v>
       </c>
@@ -16327,7 +16329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A239" t="s">
         <v>1096</v>
       </c>
@@ -16380,7 +16382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A240" t="s">
         <v>1096</v>
       </c>
@@ -16433,7 +16435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A241" t="s">
         <v>1096</v>
       </c>
@@ -16486,7 +16488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A242" t="s">
         <v>1096</v>
       </c>
@@ -16539,7 +16541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A243" t="s">
         <v>1096</v>
       </c>
@@ -16592,7 +16594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A244" t="s">
         <v>1096</v>
       </c>
@@ -16645,7 +16647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A245" t="s">
         <v>1096</v>
       </c>
@@ -16698,7 +16700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A246" t="s">
         <v>1096</v>
       </c>
@@ -16751,7 +16753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A247" t="s">
         <v>1096</v>
       </c>
@@ -16804,7 +16806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A248" t="s">
         <v>1096</v>
       </c>
@@ -16857,7 +16859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A249" t="s">
         <v>1096</v>
       </c>
@@ -16910,7 +16912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A250" t="s">
         <v>1096</v>
       </c>
@@ -16963,7 +16965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A251" t="s">
         <v>1096</v>
       </c>
@@ -17016,7 +17018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A252" t="s">
         <v>1096</v>
       </c>
@@ -17069,7 +17071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A253" t="s">
         <v>1096</v>
       </c>
@@ -17122,7 +17124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A254" t="s">
         <v>1096</v>
       </c>
@@ -17175,7 +17177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A255" t="s">
         <v>1096</v>
       </c>
@@ -17228,7 +17230,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A256" t="s">
         <v>1096</v>
       </c>
@@ -17281,7 +17283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A257" t="s">
         <v>1096</v>
       </c>
@@ -17334,7 +17336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A258" t="s">
         <v>1096</v>
       </c>
@@ -17387,7 +17389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A259" t="s">
         <v>1096</v>
       </c>
@@ -17440,7 +17442,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A260" t="s">
         <v>1096</v>
       </c>
@@ -17493,7 +17495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A261" t="s">
         <v>1096</v>
       </c>
@@ -17546,7 +17548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A262" t="s">
         <v>1096</v>
       </c>
@@ -17599,7 +17601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A263" t="s">
         <v>1096</v>
       </c>
@@ -17652,7 +17654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A264" t="s">
         <v>1096</v>
       </c>
@@ -17705,7 +17707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A265" t="s">
         <v>1096</v>
       </c>
@@ -17758,7 +17760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A266" t="s">
         <v>1096</v>
       </c>
@@ -17811,7 +17813,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A267" t="s">
         <v>1096</v>
       </c>
@@ -17864,7 +17866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A268" t="s">
         <v>1096</v>
       </c>
@@ -17917,7 +17919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A269" t="s">
         <v>1096</v>
       </c>
@@ -17970,7 +17972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A270" t="s">
         <v>1096</v>
       </c>
@@ -18023,7 +18025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A271" t="s">
         <v>1096</v>
       </c>
@@ -18076,7 +18078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A272" t="s">
         <v>1096</v>
       </c>
@@ -18129,7 +18131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A273" t="s">
         <v>1096</v>
       </c>
@@ -18182,7 +18184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A274" t="s">
         <v>1096</v>
       </c>
@@ -18235,7 +18237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A275" t="s">
         <v>1096</v>
       </c>
@@ -18288,7 +18290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A276" t="s">
         <v>1096</v>
       </c>
@@ -18341,7 +18343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A277" t="s">
         <v>1096</v>
       </c>
@@ -18394,7 +18396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="278" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A278" t="s">
         <v>1096</v>
       </c>
@@ -18447,7 +18449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A279" t="s">
         <v>1096</v>
       </c>
@@ -18500,7 +18502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="280" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A280" t="s">
         <v>1096</v>
       </c>
@@ -18553,7 +18555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A281" t="s">
         <v>1096</v>
       </c>
@@ -18606,7 +18608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A282" t="s">
         <v>1096</v>
       </c>
@@ -18659,7 +18661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A283" t="s">
         <v>1096</v>
       </c>
@@ -18712,7 +18714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A284" t="s">
         <v>1096</v>
       </c>
@@ -18765,7 +18767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A285" t="s">
         <v>1096</v>
       </c>
@@ -18818,7 +18820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A286" t="s">
         <v>1096</v>
       </c>
@@ -18871,7 +18873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A287" t="s">
         <v>1096</v>
       </c>
@@ -18924,7 +18926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A288" t="s">
         <v>1096</v>
       </c>
@@ -18977,7 +18979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A289" t="s">
         <v>1096</v>
       </c>
@@ -19030,7 +19032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A290" t="s">
         <v>1096</v>
       </c>
@@ -19083,7 +19085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A291" t="s">
         <v>1096</v>
       </c>
@@ -19136,7 +19138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A292" t="s">
         <v>1096</v>
       </c>
@@ -19189,7 +19191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="293" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A293" t="s">
         <v>1096</v>
       </c>
@@ -19242,7 +19244,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A294" t="s">
         <v>1096</v>
       </c>
@@ -19295,7 +19297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A295" t="s">
         <v>1096</v>
       </c>
@@ -19348,7 +19350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A296" t="s">
         <v>1096</v>
       </c>
@@ -19401,7 +19403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A297" t="s">
         <v>1096</v>
       </c>
@@ -19454,7 +19456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A298" t="s">
         <v>1096</v>
       </c>
@@ -19507,7 +19509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A299" t="s">
         <v>1096</v>
       </c>
@@ -19560,7 +19562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="300" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A300" t="s">
         <v>1096</v>
       </c>
@@ -19613,7 +19615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="301" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A301" t="s">
         <v>1096</v>
       </c>
@@ -19666,7 +19668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="302" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A302" t="s">
         <v>1096</v>
       </c>
@@ -19719,7 +19721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="303" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A303" t="s">
         <v>1096</v>
       </c>
@@ -19772,7 +19774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="304" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A304" t="s">
         <v>1096</v>
       </c>
@@ -19825,7 +19827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="305" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A305" t="s">
         <v>1096</v>
       </c>
@@ -19878,7 +19880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="306" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A306" t="s">
         <v>1096</v>
       </c>
@@ -19931,7 +19933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="307" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A307" t="s">
         <v>1096</v>
       </c>
@@ -19984,7 +19986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A308" t="s">
         <v>1096</v>
       </c>
@@ -20037,7 +20039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A309" t="s">
         <v>1096</v>
       </c>
@@ -20090,7 +20092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="310" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A310" t="s">
         <v>1096</v>
       </c>
@@ -20143,7 +20145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="311" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A311" t="s">
         <v>1096</v>
       </c>
@@ -20196,7 +20198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="312" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A312" t="s">
         <v>1096</v>
       </c>
@@ -20249,7 +20251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="313" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A313" t="s">
         <v>1096</v>
       </c>
@@ -20302,7 +20304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A314" t="s">
         <v>1096</v>
       </c>
@@ -20355,7 +20357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="315" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A315" t="s">
         <v>1096</v>
       </c>
@@ -20408,7 +20410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="316" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A316" t="s">
         <v>1096</v>
       </c>
@@ -20461,7 +20463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="317" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A317" t="s">
         <v>1096</v>
       </c>
@@ -20514,7 +20516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A318" t="s">
         <v>1096</v>
       </c>
@@ -20567,7 +20569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A319" t="s">
         <v>1096</v>
       </c>
@@ -20620,7 +20622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="320" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A320" t="s">
         <v>1096</v>
       </c>
@@ -20673,7 +20675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="321" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A321" t="s">
         <v>1096</v>
       </c>
@@ -20726,7 +20728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="322" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A322" t="s">
         <v>1096</v>
       </c>
@@ -20779,7 +20781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="323" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A323" t="s">
         <v>1096</v>
       </c>
@@ -20832,7 +20834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="324" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A324" t="s">
         <v>1096</v>
       </c>
@@ -20885,7 +20887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="325" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A325" t="s">
         <v>1096</v>
       </c>
@@ -20938,7 +20940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="326" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A326" t="s">
         <v>1096</v>
       </c>
@@ -20991,7 +20993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="327" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A327" t="s">
         <v>1096</v>
       </c>
@@ -21044,7 +21046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="328" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A328" t="s">
         <v>1096</v>
       </c>
@@ -21097,7 +21099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="329" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A329" t="s">
         <v>1096</v>
       </c>
@@ -21150,7 +21152,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="330" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A330" t="s">
         <v>1096</v>
       </c>
@@ -21203,7 +21205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="331" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A331" t="s">
         <v>1096</v>
       </c>
@@ -21256,7 +21258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="332" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A332" t="s">
         <v>1096</v>
       </c>
@@ -21309,7 +21311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="333" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A333" t="s">
         <v>1096</v>
       </c>
@@ -21362,7 +21364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="334" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A334" t="s">
         <v>1096</v>
       </c>
@@ -21415,7 +21417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="335" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A335" t="s">
         <v>1096</v>
       </c>
@@ -21468,7 +21470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="336" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A336" t="s">
         <v>1096</v>
       </c>
@@ -21521,7 +21523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="337" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A337" t="s">
         <v>1096</v>
       </c>
@@ -21574,7 +21576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="338" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A338" t="s">
         <v>1096</v>
       </c>
@@ -21627,7 +21629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="339" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A339" t="s">
         <v>1096</v>
       </c>
@@ -21680,7 +21682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="340" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A340" t="s">
         <v>1096</v>
       </c>
@@ -21733,7 +21735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="341" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A341" t="s">
         <v>1096</v>
       </c>
@@ -21786,7 +21788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="342" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A342" t="s">
         <v>1096</v>
       </c>
@@ -21839,7 +21841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="343" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A343" t="s">
         <v>1096</v>
       </c>
@@ -21892,7 +21894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="344" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A344" t="s">
         <v>1096</v>
       </c>
@@ -21945,7 +21947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="345" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A345" t="s">
         <v>1096</v>
       </c>
@@ -21998,7 +22000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="346" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A346" t="s">
         <v>1096</v>
       </c>
@@ -22051,7 +22053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="347" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A347" t="s">
         <v>1096</v>
       </c>
@@ -22104,7 +22106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="348" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A348" t="s">
         <v>1096</v>
       </c>
@@ -22157,7 +22159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="349" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A349" t="s">
         <v>1096</v>
       </c>
@@ -22210,7 +22212,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="350" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A350" t="s">
         <v>1096</v>
       </c>
@@ -22263,7 +22265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="351" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A351" t="s">
         <v>1096</v>
       </c>
@@ -22316,7 +22318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A352" t="s">
         <v>1096</v>
       </c>
@@ -22369,7 +22371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="353" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A353" t="s">
         <v>1096</v>
       </c>
@@ -22422,7 +22424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="354" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A354" t="s">
         <v>1096</v>
       </c>
@@ -22475,7 +22477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="355" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A355" t="s">
         <v>1096</v>
       </c>
@@ -22528,7 +22530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="356" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A356" t="s">
         <v>1096</v>
       </c>
@@ -22581,7 +22583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="357" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A357" t="s">
         <v>1096</v>
       </c>
@@ -22634,7 +22636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="358" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A358" t="s">
         <v>1096</v>
       </c>
@@ -22687,7 +22689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="359" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A359" t="s">
         <v>1096</v>
       </c>
@@ -22740,7 +22742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="360" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A360" t="s">
         <v>1096</v>
       </c>
@@ -22793,7 +22795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="361" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A361" t="s">
         <v>1096</v>
       </c>
@@ -22846,7 +22848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="362" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A362" t="s">
         <v>1096</v>
       </c>
@@ -22899,7 +22901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="363" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A363" t="s">
         <v>1096</v>
       </c>
@@ -22952,7 +22954,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="364" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A364" t="s">
         <v>1096</v>
       </c>
@@ -23005,7 +23007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="365" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A365" t="s">
         <v>1096</v>
       </c>
@@ -23058,7 +23060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="366" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A366" t="s">
         <v>1096</v>
       </c>
@@ -23111,7 +23113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="367" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A367" t="s">
         <v>1096</v>
       </c>
@@ -23164,7 +23166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="368" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A368" t="s">
         <v>1096</v>
       </c>
@@ -23217,7 +23219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="369" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A369" t="s">
         <v>1096</v>
       </c>
@@ -23270,7 +23272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="370" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A370" t="s">
         <v>1096</v>
       </c>
@@ -23323,7 +23325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="371" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A371" t="s">
         <v>1096</v>
       </c>
@@ -23376,7 +23378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="372" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A372" t="s">
         <v>1096</v>
       </c>
@@ -23429,7 +23431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="373" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A373" t="s">
         <v>1096</v>
       </c>
@@ -23482,7 +23484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="374" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A374" t="s">
         <v>1096</v>
       </c>
@@ -23535,7 +23537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="375" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A375" t="s">
         <v>1096</v>
       </c>
@@ -23588,7 +23590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="376" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A376" t="s">
         <v>1096</v>
       </c>
@@ -23641,7 +23643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="377" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A377" t="s">
         <v>1096</v>
       </c>
@@ -23694,7 +23696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="378" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A378" t="s">
         <v>1096</v>
       </c>
@@ -23747,7 +23749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="379" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A379" t="s">
         <v>1096</v>
       </c>
@@ -23800,7 +23802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="380" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A380" t="s">
         <v>1096</v>
       </c>
@@ -23853,7 +23855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="381" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A381" t="s">
         <v>1096</v>
       </c>
@@ -23906,7 +23908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="382" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A382" t="s">
         <v>1096</v>
       </c>
@@ -23959,7 +23961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="383" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A383" t="s">
         <v>1096</v>
       </c>
@@ -24012,7 +24014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="384" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A384" t="s">
         <v>1096</v>
       </c>
@@ -24065,7 +24067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A385" t="s">
         <v>1096</v>
       </c>
@@ -24118,7 +24120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="386" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A386" t="s">
         <v>1096</v>
       </c>
@@ -24171,7 +24173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="387" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A387" t="s">
         <v>1096</v>
       </c>
@@ -24224,7 +24226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A388" t="s">
         <v>1096</v>
       </c>
@@ -24277,7 +24279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="389" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A389" t="s">
         <v>1096</v>
       </c>
@@ -24330,7 +24332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="390" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A390" t="s">
         <v>1096</v>
       </c>
@@ -24383,7 +24385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="391" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A391" t="s">
         <v>1096</v>
       </c>
@@ -24436,7 +24438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="392" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A392" t="s">
         <v>1096</v>
       </c>
@@ -24489,7 +24491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="393" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A393" t="s">
         <v>1096</v>
       </c>
@@ -24542,7 +24544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="394" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A394" t="s">
         <v>1096</v>
       </c>
@@ -24595,7 +24597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="395" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A395" t="s">
         <v>1096</v>
       </c>
@@ -24648,7 +24650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="396" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A396" t="s">
         <v>1096</v>
       </c>
@@ -24701,7 +24703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="397" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A397" t="s">
         <v>1096</v>
       </c>
@@ -24754,7 +24756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="398" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A398" t="s">
         <v>1096</v>
       </c>
@@ -24807,7 +24809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A399" t="s">
         <v>1096</v>
       </c>
@@ -24860,7 +24862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="400" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A400" t="s">
         <v>1096</v>
       </c>
@@ -24913,7 +24915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="401" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A401" t="s">
         <v>1096</v>
       </c>
@@ -24966,7 +24968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="402" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A402" t="s">
         <v>1096</v>
       </c>
@@ -25019,7 +25021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="403" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A403" t="s">
         <v>1096</v>
       </c>
@@ -25072,7 +25074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="404" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A404" t="s">
         <v>1096</v>
       </c>
@@ -25125,7 +25127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="405" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A405" t="s">
         <v>1096</v>
       </c>
@@ -25178,7 +25180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="406" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A406" t="s">
         <v>1096</v>
       </c>
@@ -25231,7 +25233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="407" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A407" t="s">
         <v>1096</v>
       </c>
@@ -25284,7 +25286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="408" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A408" t="s">
         <v>1096</v>
       </c>
@@ -25337,7 +25339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="409" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A409" t="s">
         <v>1096</v>
       </c>
@@ -25390,7 +25392,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="410" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A410" t="s">
         <v>1096</v>
       </c>
@@ -25443,7 +25445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="411" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A411" t="s">
         <v>1096</v>
       </c>
@@ -25496,7 +25498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="412" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A412" t="s">
         <v>1096</v>
       </c>
@@ -25549,7 +25551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="413" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A413" t="s">
         <v>1096</v>
       </c>
@@ -25602,7 +25604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="414" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A414" t="s">
         <v>1096</v>
       </c>
@@ -25655,7 +25657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="415" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A415" t="s">
         <v>1096</v>
       </c>
@@ -25708,7 +25710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="416" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A416" t="s">
         <v>1096</v>
       </c>
@@ -25761,7 +25763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="417" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A417" t="s">
         <v>1096</v>
       </c>
@@ -25814,7 +25816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="418" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A418" t="s">
         <v>1096</v>
       </c>
@@ -25867,7 +25869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="419" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A419" t="s">
         <v>1096</v>
       </c>
@@ -25920,7 +25922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="420" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A420" t="s">
         <v>1096</v>
       </c>
@@ -25973,7 +25975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="421" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A421" t="s">
         <v>1096</v>
       </c>
@@ -26026,7 +26028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="422" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A422" t="s">
         <v>1096</v>
       </c>
@@ -26079,7 +26081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="423" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A423" t="s">
         <v>1096</v>
       </c>
@@ -26132,7 +26134,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="424" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A424" t="s">
         <v>1096</v>
       </c>
@@ -26185,7 +26187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="425" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A425" t="s">
         <v>1096</v>
       </c>
@@ -26238,7 +26240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="426" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A426" t="s">
         <v>1096</v>
       </c>
@@ -26291,7 +26293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="427" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A427" t="s">
         <v>1096</v>
       </c>
@@ -26344,7 +26346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="428" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A428" t="s">
         <v>1096</v>
       </c>
@@ -26397,7 +26399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="429" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A429" t="s">
         <v>1096</v>
       </c>
@@ -26450,7 +26452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="430" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A430" t="s">
         <v>1096</v>
       </c>
@@ -26503,7 +26505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="431" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A431" t="s">
         <v>1096</v>
       </c>
@@ -26556,7 +26558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="432" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A432" t="s">
         <v>1096</v>
       </c>
@@ -26609,7 +26611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="433" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A433" t="s">
         <v>1096</v>
       </c>
@@ -26662,7 +26664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="434" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A434" t="s">
         <v>1096</v>
       </c>
@@ -26715,7 +26717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="435" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A435" t="s">
         <v>1096</v>
       </c>
@@ -26768,7 +26770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="436" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A436" t="s">
         <v>1096</v>
       </c>
@@ -26821,7 +26823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="437" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A437" t="s">
         <v>1096</v>
       </c>
@@ -26874,7 +26876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="438" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A438" t="s">
         <v>1096</v>
       </c>
@@ -26927,7 +26929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="439" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A439" t="s">
         <v>1096</v>
       </c>
@@ -26980,7 +26982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="440" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A440" t="s">
         <v>1096</v>
       </c>
@@ -27033,7 +27035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="441" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A441" t="s">
         <v>1096</v>
       </c>
@@ -27086,7 +27088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="442" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A442" t="s">
         <v>1096</v>
       </c>
@@ -27139,7 +27141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="443" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A443" t="s">
         <v>1096</v>
       </c>
@@ -27192,7 +27194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="444" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A444" t="s">
         <v>1096</v>
       </c>
@@ -27245,7 +27247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="445" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A445" t="s">
         <v>1096</v>
       </c>
@@ -27298,7 +27300,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="446" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A446" t="s">
         <v>1096</v>
       </c>
@@ -27351,7 +27353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="447" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A447" t="s">
         <v>1096</v>
       </c>
@@ -27404,7 +27406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="448" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A448" t="s">
         <v>1096</v>
       </c>
@@ -27457,7 +27459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="449" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A449" t="s">
         <v>1096</v>
       </c>
@@ -27510,7 +27512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="450" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A450" t="s">
         <v>1096</v>
       </c>
@@ -27563,7 +27565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="451" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A451" t="s">
         <v>1096</v>
       </c>
@@ -27616,7 +27618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="452" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A452" t="s">
         <v>1096</v>
       </c>
@@ -27669,7 +27671,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A453" t="s">
         <v>1096</v>
       </c>
@@ -27722,7 +27724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="454" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A454" t="s">
         <v>1096</v>
       </c>
@@ -27775,7 +27777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="455" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A455" t="s">
         <v>1096</v>
       </c>
@@ -27828,7 +27830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="456" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A456" t="s">
         <v>1096</v>
       </c>
@@ -27881,7 +27883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="457" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A457" t="s">
         <v>1096</v>
       </c>
@@ -27934,7 +27936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="458" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A458" t="s">
         <v>1096</v>
       </c>
@@ -27987,7 +27989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="459" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A459" t="s">
         <v>1096</v>
       </c>
@@ -28040,7 +28042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="460" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A460" t="s">
         <v>1096</v>
       </c>
@@ -28093,7 +28095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="461" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A461" t="s">
         <v>1096</v>
       </c>
@@ -28146,7 +28148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="462" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A462" t="s">
         <v>1096</v>
       </c>
@@ -28199,7 +28201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="463" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A463" t="s">
         <v>1096</v>
       </c>
@@ -28252,7 +28254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="464" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A464" t="s">
         <v>1096</v>
       </c>
@@ -28305,7 +28307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="465" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A465" t="s">
         <v>1096</v>
       </c>
@@ -28358,7 +28360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="466" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A466" t="s">
         <v>1096</v>
       </c>
@@ -28411,7 +28413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="467" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A467" t="s">
         <v>1096</v>
       </c>
@@ -28464,7 +28466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="468" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A468" t="s">
         <v>1096</v>
       </c>
@@ -28517,7 +28519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="469" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A469" t="s">
         <v>1096</v>
       </c>
@@ -28570,7 +28572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="470" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A470" t="s">
         <v>1096</v>
       </c>
@@ -28623,7 +28625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="471" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A471" t="s">
         <v>1096</v>
       </c>
@@ -28676,7 +28678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="472" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A472" t="s">
         <v>1096</v>
       </c>
@@ -28729,7 +28731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="473" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A473" t="s">
         <v>1096</v>
       </c>
@@ -28782,7 +28784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="474" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A474" t="s">
         <v>1096</v>
       </c>
@@ -28835,7 +28837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="475" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A475" t="s">
         <v>1096</v>
       </c>
@@ -28888,7 +28890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="476" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A476" t="s">
         <v>1096</v>
       </c>
@@ -28941,7 +28943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="477" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A477" t="s">
         <v>1096</v>
       </c>
@@ -28994,7 +28996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="478" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A478" t="s">
         <v>1096</v>
       </c>
@@ -29047,7 +29049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="479" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A479" t="s">
         <v>1096</v>
       </c>
@@ -29100,7 +29102,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="480" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A480" t="s">
         <v>1096</v>
       </c>
@@ -29153,7 +29155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="481" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A481" t="s">
         <v>1096</v>
       </c>
@@ -29206,7 +29208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="482" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A482" t="s">
         <v>1096</v>
       </c>
@@ -29259,7 +29261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="483" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A483" t="s">
         <v>1096</v>
       </c>
@@ -29312,7 +29314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="484" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A484" t="s">
         <v>1096</v>
       </c>
@@ -29365,7 +29367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="485" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A485" t="s">
         <v>1096</v>
       </c>
@@ -29418,7 +29420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="486" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A486" t="s">
         <v>1096</v>
       </c>
@@ -29471,7 +29473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="487" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A487" t="s">
         <v>1096</v>
       </c>
@@ -29524,7 +29526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="488" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A488" t="s">
         <v>1096</v>
       </c>
@@ -29577,7 +29579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="489" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A489" t="s">
         <v>1096</v>
       </c>
@@ -29630,7 +29632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="490" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A490" t="s">
         <v>1096</v>
       </c>
@@ -29683,7 +29685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="491" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A491" t="s">
         <v>1096</v>
       </c>
@@ -29736,7 +29738,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="492" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A492" t="s">
         <v>1096</v>
       </c>
@@ -29789,7 +29791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="493" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A493" t="s">
         <v>1096</v>
       </c>
@@ -29842,7 +29844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="494" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A494" t="s">
         <v>1096</v>
       </c>
@@ -29895,7 +29897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="495" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A495" t="s">
         <v>1096</v>
       </c>
@@ -29948,7 +29950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="496" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A496" t="s">
         <v>1096</v>
       </c>
@@ -30001,7 +30003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A497" t="s">
         <v>1096</v>
       </c>
@@ -30054,7 +30056,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="498" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A498" t="s">
         <v>1096</v>
       </c>
@@ -30107,7 +30109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="499" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A499" t="s">
         <v>1096</v>
       </c>
@@ -30160,7 +30162,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="500" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A500" t="s">
         <v>1096</v>
       </c>
@@ -30213,7 +30215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="501" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A501" t="s">
         <v>1096</v>
       </c>
@@ -30266,7 +30268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="502" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A502" t="s">
         <v>1096</v>
       </c>
@@ -30319,7 +30321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="503" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A503" t="s">
         <v>1096</v>
       </c>
@@ -30372,7 +30374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="504" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A504" t="s">
         <v>1096</v>
       </c>
@@ -30425,7 +30427,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="505" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A505" t="s">
         <v>1096</v>
       </c>
@@ -30478,7 +30480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="506" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A506" t="s">
         <v>1096</v>
       </c>
@@ -30531,7 +30533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="507" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A507" t="s">
         <v>1096</v>
       </c>
@@ -30584,7 +30586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="508" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A508" t="s">
         <v>1096</v>
       </c>
@@ -30637,7 +30639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="509" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A509" t="s">
         <v>1096</v>
       </c>
@@ -30690,7 +30692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="510" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A510" t="s">
         <v>1096</v>
       </c>
@@ -30743,7 +30745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="511" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A511" t="s">
         <v>1096</v>
       </c>
@@ -30796,7 +30798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="512" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A512" t="s">
         <v>1096</v>
       </c>
@@ -30849,7 +30851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A513" t="s">
         <v>1096</v>
       </c>
@@ -30902,7 +30904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A514" t="s">
         <v>1096</v>
       </c>
@@ -30955,7 +30957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="515" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A515" t="s">
         <v>1096</v>
       </c>
@@ -31008,7 +31010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="516" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A516" t="s">
         <v>1096</v>
       </c>
@@ -31061,7 +31063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="517" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A517" t="s">
         <v>1096</v>
       </c>
@@ -31114,7 +31116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="518" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A518" t="s">
         <v>1096</v>
       </c>
@@ -31167,7 +31169,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="519" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A519" t="s">
         <v>1096</v>
       </c>
@@ -31220,7 +31222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="520" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A520" t="s">
         <v>1096</v>
       </c>
@@ -31273,7 +31275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="521" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A521" t="s">
         <v>1096</v>
       </c>
@@ -31326,7 +31328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="522" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A522" t="s">
         <v>1096</v>
       </c>
@@ -31379,7 +31381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="523" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A523" t="s">
         <v>1096</v>
       </c>
@@ -31432,7 +31434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="524" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A524" t="s">
         <v>1096</v>
       </c>
@@ -31485,7 +31487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="525" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A525" t="s">
         <v>1096</v>
       </c>
@@ -31538,7 +31540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="526" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A526" t="s">
         <v>1096</v>
       </c>
@@ -31591,7 +31593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="527" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A527" t="s">
         <v>1096</v>
       </c>
@@ -31644,7 +31646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="528" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A528" t="s">
         <v>1096</v>
       </c>
@@ -31697,7 +31699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="529" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A529" t="s">
         <v>1096</v>
       </c>
@@ -31750,7 +31752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="530" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A530" t="s">
         <v>1096</v>
       </c>
@@ -31803,7 +31805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="531" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A531" t="s">
         <v>1096</v>
       </c>
@@ -31856,7 +31858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="532" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A532" t="s">
         <v>1096</v>
       </c>
@@ -31909,7 +31911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="533" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A533" t="s">
         <v>1096</v>
       </c>
@@ -31962,7 +31964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="534" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A534" t="s">
         <v>1096</v>
       </c>
@@ -32015,7 +32017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="535" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A535" t="s">
         <v>1096</v>
       </c>
@@ -32068,7 +32070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="536" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A536" t="s">
         <v>1096</v>
       </c>
@@ -32121,7 +32123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="537" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A537" t="s">
         <v>1096</v>
       </c>
@@ -32174,7 +32176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="538" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A538" t="s">
         <v>1096</v>
       </c>
@@ -32227,7 +32229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="539" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A539" t="s">
         <v>1096</v>
       </c>
@@ -32280,7 +32282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="540" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A540" t="s">
         <v>1096</v>
       </c>
@@ -32333,7 +32335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="541" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A541" t="s">
         <v>1096</v>
       </c>
@@ -32386,7 +32388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="542" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A542" t="s">
         <v>1096</v>
       </c>
@@ -32439,7 +32441,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="543" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A543" t="s">
         <v>1096</v>
       </c>
@@ -32492,7 +32494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="544" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A544" t="s">
         <v>1096</v>
       </c>
@@ -32545,7 +32547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="545" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A545" t="s">
         <v>1096</v>
       </c>
@@ -32598,7 +32600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="546" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A546" t="s">
         <v>1096</v>
       </c>
@@ -32651,7 +32653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="547" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A547" t="s">
         <v>1096</v>
       </c>
@@ -32704,7 +32706,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="548" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A548" t="s">
         <v>1096</v>
       </c>
@@ -32757,7 +32759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="549" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A549" t="s">
         <v>1096</v>
       </c>
@@ -32810,7 +32812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="550" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A550" t="s">
         <v>1096</v>
       </c>
@@ -32863,7 +32865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="551" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A551" t="s">
         <v>1096</v>
       </c>
@@ -32916,7 +32918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="552" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A552" t="s">
         <v>1096</v>
       </c>
@@ -32969,7 +32971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="553" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A553" t="s">
         <v>1096</v>
       </c>
@@ -33022,7 +33024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="554" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A554" t="s">
         <v>1096</v>
       </c>
@@ -33075,7 +33077,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="555" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A555" t="s">
         <v>1096</v>
       </c>
@@ -33128,7 +33130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="556" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A556" t="s">
         <v>1096</v>
       </c>
@@ -33181,7 +33183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="557" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A557" t="s">
         <v>1096</v>
       </c>
@@ -33234,7 +33236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="558" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A558" t="s">
         <v>1096</v>
       </c>
@@ -33287,7 +33289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="559" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A559" t="s">
         <v>1096</v>
       </c>
@@ -33340,7 +33342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="560" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A560" t="s">
         <v>1096</v>
       </c>
@@ -33393,7 +33395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="561" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A561" t="s">
         <v>1096</v>
       </c>
@@ -33446,7 +33448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="562" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A562" t="s">
         <v>1096</v>
       </c>
@@ -33499,7 +33501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="563" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A563" t="s">
         <v>1096</v>
       </c>
@@ -33552,7 +33554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="564" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A564" t="s">
         <v>1096</v>
       </c>
@@ -33605,7 +33607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="565" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A565" t="s">
         <v>1096</v>
       </c>
@@ -33658,7 +33660,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="566" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A566" t="s">
         <v>1096</v>
       </c>
@@ -33711,7 +33713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="567" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A567" t="s">
         <v>1096</v>
       </c>
@@ -33764,7 +33766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="568" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A568" t="s">
         <v>1096</v>
       </c>
@@ -33817,7 +33819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="569" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A569" t="s">
         <v>1096</v>
       </c>
@@ -33870,7 +33872,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="570" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A570" t="s">
         <v>1096</v>
       </c>
@@ -33923,7 +33925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="571" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A571" t="s">
         <v>1096</v>
       </c>
@@ -33976,7 +33978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="572" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A572" t="s">
         <v>1096</v>
       </c>
@@ -34029,7 +34031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="573" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A573" t="s">
         <v>1096</v>
       </c>
@@ -34082,7 +34084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="574" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A574" t="s">
         <v>1096</v>
       </c>
@@ -34135,7 +34137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="575" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A575" t="s">
         <v>1096</v>
       </c>
@@ -34188,7 +34190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="576" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A576" t="s">
         <v>1096</v>
       </c>
@@ -34241,7 +34243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="577" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A577" t="s">
         <v>1096</v>
       </c>
@@ -34294,7 +34296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="578" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A578" t="s">
         <v>1096</v>
       </c>
@@ -34347,7 +34349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="579" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A579" t="s">
         <v>1096</v>
       </c>
@@ -34400,7 +34402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="580" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A580" t="s">
         <v>1096</v>
       </c>
@@ -34453,7 +34455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="581" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A581" t="s">
         <v>1096</v>
       </c>
@@ -34506,7 +34508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="582" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A582" t="s">
         <v>1096</v>
       </c>
@@ -34559,7 +34561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="583" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A583" t="s">
         <v>1096</v>
       </c>
@@ -34612,7 +34614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="584" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A584" t="s">
         <v>1096</v>
       </c>
@@ -34665,7 +34667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="585" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A585" t="s">
         <v>1096</v>
       </c>
@@ -34718,7 +34720,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A586" t="s">
         <v>1096</v>
       </c>
@@ -34771,7 +34773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="587" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A587" t="s">
         <v>1096</v>
       </c>
@@ -34824,7 +34826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="588" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A588" t="s">
         <v>1096</v>
       </c>
@@ -34877,7 +34879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="589" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A589" t="s">
         <v>1096</v>
       </c>
@@ -34930,7 +34932,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="590" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A590" t="s">
         <v>1096</v>
       </c>
@@ -34983,7 +34985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="591" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A591" t="s">
         <v>1096</v>
       </c>
@@ -35036,7 +35038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="592" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A592" t="s">
         <v>1096</v>
       </c>
@@ -35089,7 +35091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="593" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A593" t="s">
         <v>1096</v>
       </c>
@@ -35142,7 +35144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="594" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A594" t="s">
         <v>1096</v>
       </c>
@@ -35195,7 +35197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="595" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A595" t="s">
         <v>1096</v>
       </c>
@@ -35248,7 +35250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="596" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A596" t="s">
         <v>1096</v>
       </c>
@@ -35301,7 +35303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="597" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A597" t="s">
         <v>1096</v>
       </c>
@@ -35354,7 +35356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="598" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A598" t="s">
         <v>1096</v>
       </c>
@@ -35407,7 +35409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="599" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A599" t="s">
         <v>1096</v>
       </c>
@@ -35460,7 +35462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="600" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A600" t="s">
         <v>1096</v>
       </c>
@@ -35513,7 +35515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="601" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A601" t="s">
         <v>1096</v>
       </c>
@@ -35566,7 +35568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="602" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A602" t="s">
         <v>1096</v>
       </c>
@@ -35619,7 +35621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="603" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A603" t="s">
         <v>1096</v>
       </c>
@@ -35672,7 +35674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="604" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A604" t="s">
         <v>1096</v>
       </c>
@@ -35725,7 +35727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="605" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A605" t="s">
         <v>1096</v>
       </c>
@@ -35778,7 +35780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="606" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A606" t="s">
         <v>1096</v>
       </c>
@@ -35831,7 +35833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="607" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A607" t="s">
         <v>1096</v>
       </c>
@@ -35884,7 +35886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="608" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A608" t="s">
         <v>1096</v>
       </c>
@@ -35937,7 +35939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="609" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A609" t="s">
         <v>1096</v>
       </c>
@@ -35990,7 +35992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="610" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A610" t="s">
         <v>1096</v>
       </c>
@@ -36043,7 +36045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="611" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A611" t="s">
         <v>1096</v>
       </c>
@@ -36096,7 +36098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="612" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A612" t="s">
         <v>1096</v>
       </c>
@@ -36149,7 +36151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="613" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A613" t="s">
         <v>1096</v>
       </c>
@@ -36202,7 +36204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="614" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A614" t="s">
         <v>1096</v>
       </c>
@@ -36255,7 +36257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="615" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A615" t="s">
         <v>1096</v>
       </c>
@@ -36308,7 +36310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="616" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A616" t="s">
         <v>1096</v>
       </c>
@@ -36361,7 +36363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="617" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A617" t="s">
         <v>1096</v>
       </c>
@@ -36414,7 +36416,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="618" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A618" t="s">
         <v>1096</v>
       </c>
@@ -36467,7 +36469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="619" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A619" t="s">
         <v>1096</v>
       </c>
@@ -36520,7 +36522,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="620" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A620" t="s">
         <v>1096</v>
       </c>
@@ -36573,7 +36575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="621" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A621" t="s">
         <v>1096</v>
       </c>
@@ -36626,7 +36628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="622" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A622" t="s">
         <v>1096</v>
       </c>
@@ -36679,7 +36681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="623" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A623" t="s">
         <v>1096</v>
       </c>
@@ -36732,7 +36734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="624" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A624" t="s">
         <v>1096</v>
       </c>
@@ -36785,7 +36787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="625" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A625" t="s">
         <v>1096</v>
       </c>
@@ -36838,7 +36840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="626" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A626" t="s">
         <v>1096</v>
       </c>
@@ -36891,7 +36893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="627" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A627" t="s">
         <v>1096</v>
       </c>
@@ -36944,7 +36946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="628" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A628" t="s">
         <v>1096</v>
       </c>
@@ -36997,7 +36999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="629" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A629" t="s">
         <v>1096</v>
       </c>
@@ -37050,7 +37052,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="630" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A630" t="s">
         <v>1096</v>
       </c>
@@ -37103,7 +37105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="631" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A631" t="s">
         <v>1096</v>
       </c>
@@ -37156,7 +37158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="632" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A632" t="s">
         <v>1096</v>
       </c>
@@ -37209,7 +37211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="633" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A633" t="s">
         <v>1096</v>
       </c>
@@ -37262,7 +37264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="634" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A634" t="s">
         <v>1096</v>
       </c>
@@ -37315,7 +37317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="635" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A635" t="s">
         <v>1096</v>
       </c>
@@ -37368,7 +37370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="636" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A636" t="s">
         <v>1096</v>
       </c>
@@ -37421,7 +37423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="637" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A637" t="s">
         <v>1096</v>
       </c>
@@ -37474,7 +37476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="638" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A638" t="s">
         <v>1096</v>
       </c>
@@ -37527,7 +37529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="639" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A639" t="s">
         <v>1096</v>
       </c>
@@ -37580,7 +37582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="640" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A640" t="s">
         <v>1096</v>
       </c>
@@ -37633,7 +37635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="641" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A641" t="s">
         <v>1096</v>
       </c>
@@ -37686,7 +37688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="642" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A642" t="s">
         <v>1096</v>
       </c>
@@ -37739,7 +37741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="643" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A643" t="s">
         <v>1096</v>
       </c>
@@ -37792,7 +37794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="644" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A644" t="s">
         <v>1096</v>
       </c>
@@ -37845,7 +37847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="645" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A645" t="s">
         <v>1096</v>
       </c>
@@ -37898,7 +37900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="646" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A646" t="s">
         <v>1096</v>
       </c>
@@ -37951,7 +37953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="647" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A647" t="s">
         <v>1096</v>
       </c>
@@ -38004,7 +38006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="648" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A648" t="s">
         <v>1096</v>
       </c>
@@ -38057,7 +38059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="649" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A649" t="s">
         <v>1096</v>
       </c>
@@ -38110,7 +38112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="650" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A650" t="s">
         <v>1096</v>
       </c>
@@ -38163,7 +38165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="651" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A651" t="s">
         <v>1096</v>
       </c>
@@ -38216,7 +38218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="652" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A652" t="s">
         <v>1096</v>
       </c>
@@ -38269,7 +38271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="653" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A653" t="s">
         <v>1096</v>
       </c>
@@ -38322,7 +38324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="654" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A654" t="s">
         <v>1096</v>
       </c>
@@ -38375,7 +38377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="655" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A655" t="s">
         <v>1096</v>
       </c>
@@ -38428,7 +38430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="656" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A656" t="s">
         <v>1096</v>
       </c>
@@ -38481,7 +38483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="657" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A657" t="s">
         <v>1096</v>
       </c>
@@ -38534,7 +38536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="658" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A658" t="s">
         <v>1096</v>
       </c>
@@ -38587,7 +38589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="659" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A659" t="s">
         <v>1096</v>
       </c>
@@ -38640,7 +38642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="660" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A660" t="s">
         <v>1096</v>
       </c>
@@ -38693,7 +38695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="661" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A661" t="s">
         <v>1096</v>
       </c>
@@ -38746,7 +38748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="662" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A662" t="s">
         <v>1096</v>
       </c>
@@ -38799,7 +38801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="663" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A663" t="s">
         <v>1096</v>
       </c>
@@ -38852,7 +38854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="664" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A664" t="s">
         <v>1096</v>
       </c>
@@ -38905,7 +38907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="665" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A665" t="s">
         <v>1096</v>
       </c>
@@ -38958,7 +38960,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="666" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A666" t="s">
         <v>1096</v>
       </c>
@@ -39011,7 +39013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="667" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A667" t="s">
         <v>1096</v>
       </c>
@@ -39064,7 +39066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="668" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A668" t="s">
         <v>1096</v>
       </c>
@@ -39117,7 +39119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="669" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A669" t="s">
         <v>1096</v>
       </c>
@@ -39170,7 +39172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="670" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A670" t="s">
         <v>1096</v>
       </c>
@@ -39223,7 +39225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="671" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A671" t="s">
         <v>1096</v>
       </c>
@@ -39276,7 +39278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="672" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A672" t="s">
         <v>1096</v>
       </c>
@@ -39329,7 +39331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="673" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A673" t="s">
         <v>1096</v>
       </c>
@@ -39382,7 +39384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="674" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A674" t="s">
         <v>1096</v>
       </c>
@@ -39435,7 +39437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="675" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A675" t="s">
         <v>1096</v>
       </c>
@@ -39488,7 +39490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="676" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A676" t="s">
         <v>1096</v>
       </c>
@@ -39541,7 +39543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="677" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A677" t="s">
         <v>1096</v>
       </c>
@@ -39594,7 +39596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="678" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A678" t="s">
         <v>1096</v>
       </c>
@@ -39647,7 +39649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="679" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A679" t="s">
         <v>1096</v>
       </c>
@@ -39700,7 +39702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="680" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A680" t="s">
         <v>1096</v>
       </c>
@@ -39753,7 +39755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="681" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A681" t="s">
         <v>1096</v>
       </c>
@@ -39806,7 +39808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="682" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A682" t="s">
         <v>1096</v>
       </c>
@@ -39859,7 +39861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="683" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A683" t="s">
         <v>1096</v>
       </c>
@@ -39912,7 +39914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="684" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A684" t="s">
         <v>1096</v>
       </c>
@@ -39965,7 +39967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="685" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A685" t="s">
         <v>1096</v>
       </c>
@@ -40018,7 +40020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="686" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A686" t="s">
         <v>1096</v>
       </c>
@@ -40071,7 +40073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="687" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A687" t="s">
         <v>1096</v>
       </c>
@@ -40124,7 +40126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="688" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A688" t="s">
         <v>1096</v>
       </c>
@@ -40177,7 +40179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="689" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A689" t="s">
         <v>1096</v>
       </c>
@@ -40230,7 +40232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="690" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A690" t="s">
         <v>1096</v>
       </c>
@@ -40283,7 +40285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="691" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A691" t="s">
         <v>1096</v>
       </c>
@@ -40336,7 +40338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="692" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A692" t="s">
         <v>1096</v>
       </c>
@@ -40389,7 +40391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="693" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A693" t="s">
         <v>1096</v>
       </c>
@@ -40442,7 +40444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="694" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A694" t="s">
         <v>1096</v>
       </c>
@@ -40495,7 +40497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="695" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A695" t="s">
         <v>1096</v>
       </c>
@@ -40548,7 +40550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="696" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A696" t="s">
         <v>1096</v>
       </c>
@@ -40601,7 +40603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="697" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A697" t="s">
         <v>1096</v>
       </c>
@@ -40654,7 +40656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="698" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A698" t="s">
         <v>1096</v>
       </c>
@@ -40707,7 +40709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="699" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A699" t="s">
         <v>1096</v>
       </c>
@@ -40760,7 +40762,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="700" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A700" t="s">
         <v>1096</v>
       </c>
@@ -40813,7 +40815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="701" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A701" t="s">
         <v>1096</v>
       </c>
@@ -40866,7 +40868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="702" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A702" t="s">
         <v>1096</v>
       </c>
@@ -40919,7 +40921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="703" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A703" t="s">
         <v>1096</v>
       </c>
@@ -40972,7 +40974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="704" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A704" t="s">
         <v>1096</v>
       </c>
@@ -41025,7 +41027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="705" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A705" t="s">
         <v>1096</v>
       </c>
@@ -41078,7 +41080,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="706" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A706" t="s">
         <v>1096</v>
       </c>
@@ -41131,7 +41133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="707" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A707" t="s">
         <v>1096</v>
       </c>
@@ -41184,7 +41186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="708" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A708" t="s">
         <v>1096</v>
       </c>
@@ -41237,7 +41239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="709" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A709" t="s">
         <v>1096</v>
       </c>
@@ -41290,7 +41292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="710" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A710" t="s">
         <v>1096</v>
       </c>
@@ -41343,7 +41345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="711" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A711" t="s">
         <v>1096</v>
       </c>
@@ -41396,7 +41398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="712" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A712" t="s">
         <v>1096</v>
       </c>
@@ -41449,7 +41451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="713" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A713" t="s">
         <v>1096</v>
       </c>
@@ -41502,7 +41504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="714" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A714" t="s">
         <v>1096</v>
       </c>
@@ -41555,7 +41557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="715" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A715" t="s">
         <v>1096</v>
       </c>
@@ -41608,7 +41610,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="716" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A716" t="s">
         <v>1096</v>
       </c>
@@ -41661,7 +41663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="717" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A717" t="s">
         <v>1096</v>
       </c>
@@ -41714,7 +41716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="718" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A718" t="s">
         <v>1096</v>
       </c>
@@ -41767,7 +41769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="719" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A719" t="s">
         <v>1096</v>
       </c>
@@ -41820,7 +41822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="720" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A720" t="s">
         <v>1096</v>
       </c>
@@ -41873,7 +41875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="721" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A721" t="s">
         <v>1096</v>
       </c>
@@ -41926,7 +41928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="722" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A722" t="s">
         <v>1096</v>
       </c>
@@ -41979,7 +41981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="723" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A723" t="s">
         <v>1096</v>
       </c>
@@ -42032,7 +42034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="724" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A724" t="s">
         <v>1096</v>
       </c>
@@ -42085,7 +42087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="725" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A725" t="s">
         <v>1096</v>
       </c>
@@ -42138,7 +42140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="726" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A726" t="s">
         <v>1096</v>
       </c>
@@ -42191,7 +42193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="727" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A727" t="s">
         <v>1096</v>
       </c>
@@ -42244,7 +42246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="728" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A728" t="s">
         <v>1096</v>
       </c>
@@ -42297,7 +42299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="729" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A729" t="s">
         <v>1096</v>
       </c>
@@ -42350,7 +42352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="730" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A730" t="s">
         <v>1096</v>
       </c>
@@ -42403,7 +42405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="731" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A731" t="s">
         <v>1096</v>
       </c>
@@ -42456,7 +42458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="732" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A732" t="s">
         <v>1096</v>
       </c>
@@ -42509,7 +42511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="733" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A733" t="s">
         <v>1096</v>
       </c>
@@ -42562,7 +42564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="734" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A734" t="s">
         <v>1096</v>
       </c>
@@ -42615,7 +42617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="735" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A735" t="s">
         <v>1096</v>
       </c>
@@ -42668,7 +42670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="736" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A736" t="s">
         <v>1096</v>
       </c>
@@ -42721,7 +42723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="737" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A737" t="s">
         <v>1096</v>
       </c>
@@ -42774,7 +42776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="738" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A738" t="s">
         <v>1096</v>
       </c>
@@ -42827,7 +42829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="739" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A739" t="s">
         <v>1096</v>
       </c>
@@ -42880,7 +42882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="740" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A740" t="s">
         <v>1096</v>
       </c>
@@ -42933,7 +42935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="741" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A741" t="s">
         <v>1096</v>
       </c>
@@ -42986,7 +42988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="742" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A742" t="s">
         <v>1096</v>
       </c>
@@ -43039,7 +43041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="743" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A743" t="s">
         <v>1096</v>
       </c>
@@ -43092,7 +43094,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="744" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A744" t="s">
         <v>1096</v>
       </c>
@@ -43145,7 +43147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="745" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A745" t="s">
         <v>1096</v>
       </c>
@@ -43198,7 +43200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="746" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A746" t="s">
         <v>1096</v>
       </c>
@@ -43251,7 +43253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="747" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A747" t="s">
         <v>1096</v>
       </c>
@@ -43304,7 +43306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="748" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A748" t="s">
         <v>1096</v>
       </c>
@@ -43357,7 +43359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="749" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A749" t="s">
         <v>1096</v>
       </c>
@@ -43410,7 +43412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="750" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A750" t="s">
         <v>1096</v>
       </c>
@@ -43463,7 +43465,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="751" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A751" t="s">
         <v>1096</v>
       </c>
@@ -43516,7 +43518,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="752" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A752" t="s">
         <v>1096</v>
       </c>
@@ -43569,7 +43571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="753" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A753" t="s">
         <v>1096</v>
       </c>
@@ -43622,7 +43624,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="754" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A754" t="s">
         <v>1096</v>
       </c>
@@ -43675,7 +43677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="755" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A755" t="s">
         <v>1096</v>
       </c>
@@ -43728,7 +43730,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="756" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A756" t="s">
         <v>1096</v>
       </c>
@@ -43781,7 +43783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="757" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A757" t="s">
         <v>1096</v>
       </c>
@@ -43834,7 +43836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="758" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A758" t="s">
         <v>1096</v>
       </c>
@@ -43887,7 +43889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="759" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A759" t="s">
         <v>1096</v>
       </c>
@@ -43940,7 +43942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="760" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A760" t="s">
         <v>1096</v>
       </c>
@@ -43993,7 +43995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="761" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A761" t="s">
         <v>1096</v>
       </c>
@@ -44046,7 +44048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="762" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A762" t="s">
         <v>1096</v>
       </c>
@@ -44099,7 +44101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="763" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A763" t="s">
         <v>1096</v>
       </c>
@@ -44152,7 +44154,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="764" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A764" t="s">
         <v>1096</v>
       </c>
@@ -44205,7 +44207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="765" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A765" t="s">
         <v>1096</v>
       </c>
@@ -44258,7 +44260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="766" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A766" t="s">
         <v>1096</v>
       </c>
@@ -44311,7 +44313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="767" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A767" t="s">
         <v>1096</v>
       </c>
@@ -44364,7 +44366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="768" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A768" t="s">
         <v>1096</v>
       </c>
@@ -44417,7 +44419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="769" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A769" t="s">
         <v>1096</v>
       </c>
@@ -44470,7 +44472,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="770" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A770" t="s">
         <v>1096</v>
       </c>
@@ -44523,7 +44525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="771" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A771" t="s">
         <v>1096</v>
       </c>
@@ -44576,7 +44578,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="772" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A772" t="s">
         <v>1096</v>
       </c>
@@ -44629,7 +44631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="773" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A773" t="s">
         <v>1096</v>
       </c>
@@ -44682,7 +44684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="774" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A774" t="s">
         <v>1096</v>
       </c>
@@ -44735,7 +44737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="775" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A775" t="s">
         <v>1096</v>
       </c>
@@ -44788,7 +44790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="776" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A776" t="s">
         <v>1096</v>
       </c>
@@ -44841,7 +44843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="777" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A777" t="s">
         <v>1096</v>
       </c>
@@ -44894,7 +44896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="778" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A778" t="s">
         <v>1096</v>
       </c>
@@ -44947,7 +44949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="779" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A779" t="s">
         <v>1096</v>
       </c>
@@ -45000,7 +45002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="780" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A780" t="s">
         <v>1096</v>
       </c>
@@ -45053,7 +45055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="781" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A781" t="s">
         <v>1096</v>
       </c>
@@ -45106,7 +45108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="782" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A782" t="s">
         <v>1096</v>
       </c>
@@ -45159,7 +45161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="783" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A783" t="s">
         <v>1096</v>
       </c>
@@ -45212,7 +45214,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="784" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A784" t="s">
         <v>1096</v>
       </c>
@@ -45265,7 +45267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="785" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A785" t="s">
         <v>1096</v>
       </c>
@@ -45318,7 +45320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="786" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A786" t="s">
         <v>1096</v>
       </c>
@@ -45371,7 +45373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="787" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A787" t="s">
         <v>1096</v>
       </c>
@@ -45424,7 +45426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="788" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A788" t="s">
         <v>1096</v>
       </c>
@@ -45477,7 +45479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="789" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A789" t="s">
         <v>1096</v>
       </c>
@@ -45530,7 +45532,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="790" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A790" t="s">
         <v>1096</v>
       </c>
@@ -45583,7 +45585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="791" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A791" t="s">
         <v>1096</v>
       </c>
@@ -45636,7 +45638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="792" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A792" t="s">
         <v>1096</v>
       </c>
@@ -45689,7 +45691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="793" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A793" t="s">
         <v>1096</v>
       </c>
@@ -45742,7 +45744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="794" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A794" t="s">
         <v>1096</v>
       </c>
@@ -45795,7 +45797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="795" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A795" t="s">
         <v>1096</v>
       </c>
@@ -45848,7 +45850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="796" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A796" t="s">
         <v>1096</v>
       </c>
@@ -45901,7 +45903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="797" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A797" t="s">
         <v>1096</v>
       </c>
@@ -45954,7 +45956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="798" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A798" t="s">
         <v>1096</v>
       </c>
@@ -46007,7 +46009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="799" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A799" t="s">
         <v>1096</v>
       </c>
@@ -46060,7 +46062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="800" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A800" t="s">
         <v>1096</v>
       </c>
@@ -46113,7 +46115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="801" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A801" t="s">
         <v>1096</v>
       </c>
@@ -46166,7 +46168,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="802" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A802" t="s">
         <v>1096</v>
       </c>
@@ -46219,7 +46221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="803" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A803" t="s">
         <v>1096</v>
       </c>
@@ -46272,7 +46274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="804" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A804" t="s">
         <v>1096</v>
       </c>
@@ -46325,7 +46327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="805" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A805" t="s">
         <v>1096</v>
       </c>
@@ -46378,7 +46380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="806" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A806" t="s">
         <v>1096</v>
       </c>
@@ -46431,7 +46433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="807" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A807" t="s">
         <v>1096</v>
       </c>
@@ -46484,7 +46486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="808" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A808" t="s">
         <v>1096</v>
       </c>
@@ -46537,7 +46539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="809" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A809" t="s">
         <v>1096</v>
       </c>
@@ -46590,7 +46592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="810" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A810" t="s">
         <v>1096</v>
       </c>
@@ -46643,7 +46645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="811" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A811" t="s">
         <v>1096</v>
       </c>
@@ -46696,7 +46698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="812" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A812" t="s">
         <v>1096</v>
       </c>
@@ -46749,7 +46751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="813" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A813" t="s">
         <v>1096</v>
       </c>
@@ -46802,7 +46804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="814" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A814" t="s">
         <v>1096</v>
       </c>
@@ -46855,7 +46857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="815" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A815" t="s">
         <v>1096</v>
       </c>
@@ -46908,7 +46910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="816" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A816" t="s">
         <v>1096</v>
       </c>
@@ -46961,7 +46963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="817" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A817" t="s">
         <v>1096</v>
       </c>
@@ -47014,7 +47016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="818" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A818" t="s">
         <v>1096</v>
       </c>
@@ -47067,7 +47069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="819" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A819" t="s">
         <v>1096</v>
       </c>
@@ -47120,7 +47122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="820" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A820" t="s">
         <v>1096</v>
       </c>
@@ -47173,7 +47175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="821" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A821" t="s">
         <v>1096</v>
       </c>
@@ -47226,7 +47228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="822" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A822" t="s">
         <v>1096</v>
       </c>
@@ -47279,7 +47281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="823" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A823" t="s">
         <v>1096</v>
       </c>
@@ -47332,7 +47334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="824" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A824" t="s">
         <v>1096</v>
       </c>
@@ -47385,7 +47387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="825" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A825" t="s">
         <v>1096</v>
       </c>
@@ -47438,7 +47440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="826" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A826" t="s">
         <v>1096</v>
       </c>
@@ -47491,7 +47493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="827" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A827" t="s">
         <v>1096</v>
       </c>
@@ -47544,7 +47546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="828" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A828" t="s">
         <v>1096</v>
       </c>
@@ -47597,7 +47599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="829" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A829" t="s">
         <v>1096</v>
       </c>
@@ -47650,7 +47652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="830" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A830" t="s">
         <v>1096</v>
       </c>
@@ -47703,7 +47705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="831" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A831" t="s">
         <v>1096</v>
       </c>
@@ -47756,7 +47758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="832" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="832" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A832" t="s">
         <v>1096</v>
       </c>
@@ -47809,7 +47811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="833" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="833" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A833" t="s">
         <v>1096</v>
       </c>
@@ -47862,7 +47864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="834" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="834" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A834" t="s">
         <v>1096</v>
       </c>
@@ -47915,7 +47917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="835" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="835" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A835" t="s">
         <v>1096</v>
       </c>
@@ -47968,7 +47970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="836" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="836" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A836" t="s">
         <v>1096</v>
       </c>
@@ -48021,7 +48023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="837" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="837" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A837" t="s">
         <v>1096</v>
       </c>
@@ -48074,7 +48076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="838" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="838" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A838" t="s">
         <v>1096</v>
       </c>
@@ -48127,7 +48129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="839" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="839" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A839" t="s">
         <v>1096</v>
       </c>
@@ -48180,7 +48182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="840" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="840" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A840" t="s">
         <v>1096</v>
       </c>
@@ -48233,7 +48235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="841" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="841" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A841" t="s">
         <v>1096</v>
       </c>
@@ -48286,7 +48288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="842" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="842" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A842" t="s">
         <v>1096</v>
       </c>
@@ -48339,7 +48341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="843" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="843" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A843" t="s">
         <v>1096</v>
       </c>
@@ -48392,7 +48394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="844" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="844" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A844" t="s">
         <v>1096</v>
       </c>
@@ -48445,7 +48447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="845" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="845" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A845" t="s">
         <v>1096</v>
       </c>
@@ -48498,7 +48500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="846" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="846" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A846" t="s">
         <v>1096</v>
       </c>
@@ -48551,7 +48553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="847" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="847" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A847" t="s">
         <v>1096</v>
       </c>
@@ -48604,7 +48606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="848" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="848" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A848" t="s">
         <v>1096</v>
       </c>
@@ -48657,7 +48659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="849" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="849" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A849" t="s">
         <v>1096</v>
       </c>
@@ -48710,7 +48712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="850" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="850" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A850" t="s">
         <v>1096</v>
       </c>
@@ -48763,7 +48765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="851" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="851" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A851" t="s">
         <v>1096</v>
       </c>
@@ -48816,7 +48818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="852" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="852" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A852" t="s">
         <v>1096</v>
       </c>
@@ -48869,7 +48871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="853" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="853" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A853" t="s">
         <v>1096</v>
       </c>
@@ -48922,7 +48924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="854" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="854" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A854" t="s">
         <v>1096</v>
       </c>
@@ -48975,7 +48977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="855" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="855" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A855" t="s">
         <v>1096</v>
       </c>
@@ -49028,7 +49030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="856" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="856" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A856" t="s">
         <v>1096</v>
       </c>
@@ -49081,7 +49083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="857" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="857" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A857" t="s">
         <v>1096</v>
       </c>
@@ -49134,7 +49136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="858" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="858" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A858" t="s">
         <v>1096</v>
       </c>
@@ -49187,7 +49189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="859" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="859" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A859" t="s">
         <v>1096</v>
       </c>
@@ -49240,7 +49242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="860" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="860" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A860" t="s">
         <v>1096</v>
       </c>
@@ -49293,7 +49295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="861" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="861" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A861" t="s">
         <v>1096</v>
       </c>
@@ -49346,7 +49348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="862" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="862" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A862" t="s">
         <v>1096</v>
       </c>
@@ -49399,7 +49401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="863" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="863" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A863" t="s">
         <v>1096</v>
       </c>
@@ -49452,7 +49454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="864" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="864" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A864" t="s">
         <v>1096</v>
       </c>
@@ -49505,7 +49507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="865" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="865" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A865" t="s">
         <v>1096</v>
       </c>
@@ -49558,7 +49560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="866" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="866" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A866" t="s">
         <v>1096</v>
       </c>
@@ -49611,7 +49613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="867" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="867" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A867" t="s">
         <v>1096</v>
       </c>
@@ -49664,7 +49666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="868" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="868" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A868" t="s">
         <v>1096</v>
       </c>
@@ -49717,7 +49719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="869" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="869" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A869" t="s">
         <v>1096</v>
       </c>
@@ -49770,7 +49772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="870" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="870" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A870" t="s">
         <v>1096</v>
       </c>
